--- a/outputs/56921.xlsx
+++ b/outputs/56921.xlsx
@@ -164,40 +164,44 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -453,144 +457,144 @@
   <dimension ref="A1:O16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="2.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="0" width="2.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="8.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="12" style="0" width="2.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="9.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="2.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="1" width="2.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="12" style="1" width="2.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="5" t="n">
         <v>12345</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="K3" s="5"/>
+      <c r="K3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="n">
+      <c r="A4" s="7" t="n">
         <v>98321</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="G4" s="5" t="n">
+      <c r="C4" s="6"/>
+      <c r="G4" s="6" t="n">
         <v>64</v>
       </c>
-      <c r="K4" s="5" t="n">
+      <c r="K4" s="6" t="n">
         <v>64</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="7" t="n">
         <v>9449</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="K5" s="5" t="n">
+      <c r="G5" s="6"/>
+      <c r="K5" s="6" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="7" t="n">
         <v>11341</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="K6" s="5" t="n">
+      <c r="C6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="K6" s="6" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="7" t="n">
         <v>12365</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="6" t="n">
         <v>260</v>
       </c>
-      <c r="K7" s="5" t="n">
+      <c r="K7" s="6" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>12365</v>
       </c>
-      <c r="C15" s="5" t="n">
-        <f aca="false">SUMPRODUCT(--(MOD(COLUMN(C3:N3)-COLUMN(C3),4)=0)*($A$3:$A$10=B15)*(C3:N10))</f>
+      <c r="C15" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--(MOD(COLUMN(C3:N10)-COLUMN(C3),4)=0)*($A$3:$A$10=B15)*(C3:N10))</f>
         <v>294</v>
       </c>
-      <c r="G15" s="7"/>
+      <c r="G15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="8" t="n">
+      <c r="B16" s="9" t="n">
         <v>12345</v>
       </c>
-      <c r="C16" s="1" t="n">
-        <f aca="false">SUMPRODUCT(--(MOD(COLUMN(C4:N4)-COLUMN(C4),4)=0)*($A$3:$A$10=B16)*(C3:N10))</f>
+      <c r="C16" s="2" t="n">
+        <f aca="false">SUMPRODUCT(--(MOD(COLUMN(C3:N10)-COLUMN(C3),4)=0)*($A$3:$A$10=B16)*(C3:N10))</f>
         <v>511</v>
       </c>
-      <c r="G16" s="7"/>
+      <c r="G16" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/outputs/56921.xlsx
+++ b/outputs/56921.xlsx
@@ -501,7 +501,7 @@
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="n">
         <v>12345</v>
       </c>
@@ -516,7 +516,7 @@
       </c>
       <c r="K3" s="6"/>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="n">
         <v>98321</v>
       </c>
@@ -531,7 +531,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="n">
         <v>9449</v>
       </c>
@@ -546,7 +546,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="n">
         <v>11341</v>
       </c>
@@ -559,7 +559,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="n">
         <v>12365</v>
       </c>
@@ -576,22 +576,22 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="1" t="n">
         <v>12365</v>
       </c>
       <c r="C15" s="6" t="n">
-        <f aca="false">SUMPRODUCT(--(MOD(COLUMN(C3:N10)-COLUMN(C3),4)=0)*($A$3:$A$10=B15)*(C3:N10))</f>
+        <f aca="false">SUMPRODUCT(--(MOD(COLUMN(C7:N7)-COLUMN(C7),4)=0)*($A$3:$A$10=B15)*(C7:N7))</f>
         <v>294</v>
       </c>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="9" t="n">
         <v>12345</v>
       </c>
       <c r="C16" s="2" t="n">
-        <f aca="false">SUMPRODUCT(--(MOD(COLUMN(C3:N10)-COLUMN(C3),4)=0)*($A$3:$A$10=B16)*(C3:N10))</f>
+        <f aca="false">SUMPRODUCT(--(MOD(COLUMN(C3:N3)-COLUMN(C3),4)=0)*($A$3:$A$10=B16)*(C3:N3))</f>
         <v>511</v>
       </c>
       <c r="G16" s="8"/>
